--- a/data/hotel_prices.xlsx
+++ b/data/hotel_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1572,6 +1572,561 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>大床房</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>￥399</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>无障碍大床房</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>￥399</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>双床房</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>￥409</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>精选大床房</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>￥419</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>精选双床房</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>￥429</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>大床房</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>￥399</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>无障碍大床房</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>￥399</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>双床房</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>￥409</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>精选大床房</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>￥419</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>精选双床房</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>￥429</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>大床房</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>￥399</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:45:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>双床房</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>￥409</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:45:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>精选大床房</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>￥419</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:45:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>精选双床房</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>￥429</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:45:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>景观大床房</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>￥449</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:45:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/hotel_prices.xlsx
+++ b/data/hotel_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2127,6 +2127,598 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>大床房</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>￥399</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>双床房</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>￥409</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>精选大床房</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>￥419</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>桔子上海顾村公园酒店</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>9030710</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>精选双床房</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>￥429</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>上海外高桥自贸区美居酒店</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2000006</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>标准房-大床</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>￥559</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-06-24 23:52:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>上海外高桥自贸区美居酒店</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2000006</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>豪华房-双床</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>￥559</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-06-24 23:52:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>上海外高桥自贸区美居酒店</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2000006</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>豪华房-大床</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>￥589</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-06-24 23:52:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>上海外高桥自贸区美居酒店</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2000006</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>标准房-大床</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>￥479</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>上海外高桥自贸区美居酒店</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2000006</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>豪华房-大床</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>￥509</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>上海外高桥自贸区美居酒店</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2000006</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>豪华房-双床</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>￥509</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>上海外高桥自贸区美居酒店</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2000006</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>嘉宾房-大床</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>￥539</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>汉庭上海外滩九江路酒店</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>9003523</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>高级大床房A</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>￥539</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:41:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>汉庭上海外滩九江路酒店</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>9003523</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>高级大床房</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>￥599</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:41:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>汉庭上海外滩九江路酒店</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>9003523</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>商务大床房</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>￥659</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:41:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>汉庭上海外滩九江路酒店</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>9003523</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>双床房</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>￥779</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:41:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>汉庭上海外滩九江路酒店</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>9003523</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>家庭房</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>￥859</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:41:57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
